--- a/reference/PapersRef.xlsx
+++ b/reference/PapersRef.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="20730" windowHeight="8310" tabRatio="500"/>
+    <workbookView windowWidth="19890" windowHeight="9570" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -662,9 +662,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="42" formatCode="_-&quot;$&quot;* #,##0_-;\-&quot;$&quot;* #,##0_-;_-&quot;$&quot;* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
   <fonts count="23">
     <font>
@@ -674,25 +674,30 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -703,59 +708,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -771,7 +725,62 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -786,15 +795,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -808,23 +817,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -845,7 +845,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -857,13 +863,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -881,7 +911,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -893,31 +965,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -941,43 +995,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -989,43 +1007,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1036,21 +1036,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1087,13 +1072,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1115,164 +1119,160 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1607,7 +1607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:J94"/>
   <sheetFormatPr defaultColWidth="31.2833333333333" defaultRowHeight="15"/>
   <cols>
@@ -1656,7 +1656,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="45" hidden="1" customHeight="1" spans="1:8">
+    <row r="2" ht="45" customHeight="1" spans="1:8">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1679,7 +1679,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="53" hidden="1" customHeight="1" spans="1:8">
+    <row r="3" ht="53" customHeight="1" spans="1:8">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" ht="30" hidden="1" spans="1:8">
+    <row r="4" ht="30" spans="1:8">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:8">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="30" hidden="1" spans="1:7">
+    <row r="6" ht="30" spans="1:7">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="30" hidden="1" spans="1:7">
+    <row r="7" ht="30" spans="1:7">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" hidden="1" spans="1:6">
+    <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" ht="60" hidden="1" spans="1:7">
+    <row r="9" ht="60" spans="1:7">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" hidden="1" spans="1:8">
+    <row r="10" spans="1:8">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1845,7 +1845,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" ht="30" hidden="1" spans="1:7">
+    <row r="11" ht="30" spans="1:7">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1865,7 +1865,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" ht="30" hidden="1" spans="1:7">
+    <row r="12" ht="30" spans="1:7">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" ht="30" hidden="1" spans="1:7">
+    <row r="13" ht="30" spans="1:7">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" ht="30" hidden="1" spans="1:8">
+    <row r="14" ht="30" spans="1:8">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" ht="60" hidden="1" spans="1:7">
+    <row r="15" ht="60" spans="1:7">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" ht="30" hidden="1" spans="1:8">
+    <row r="16" ht="30" spans="1:8">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" ht="45" hidden="1" spans="1:7">
+    <row r="17" ht="45" spans="1:7">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" ht="30" hidden="1" spans="1:7">
+    <row r="18" ht="30" spans="1:7">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2011,7 +2011,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" ht="30" hidden="1" spans="1:7">
+    <row r="19" ht="30" spans="1:7">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" ht="30" hidden="1" spans="1:7">
+    <row r="20" ht="30" spans="1:7">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" ht="30" hidden="1" spans="1:8">
+    <row r="21" ht="30" spans="1:8">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" ht="30" hidden="1" spans="1:8">
+    <row r="22" ht="30" spans="1:8">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2106,7 +2106,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="23" ht="30" hidden="1" spans="1:8">
+    <row r="23" ht="30" spans="1:8">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2129,7 +2129,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="24" ht="45" hidden="1" spans="1:8">
+    <row r="24" ht="45" spans="1:8">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2155,7 +2155,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="25" ht="45" hidden="1" spans="1:8">
+    <row r="25" ht="45" spans="1:8">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" ht="45" hidden="1" spans="1:8">
+    <row r="26" ht="45" spans="1:8">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2204,7 +2204,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="27" ht="30" hidden="1" spans="1:9">
+    <row r="27" ht="30" spans="1:9">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2230,7 +2230,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" ht="30" hidden="1" spans="1:8">
+    <row r="28" ht="30" spans="1:8">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="29" ht="30" hidden="1" spans="1:8">
+    <row r="29" ht="30" spans="1:8">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -2276,7 +2276,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" ht="30" hidden="1" spans="1:9">
+    <row r="30" ht="30" spans="1:9">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="31" hidden="1" spans="1:8">
+    <row r="31" spans="1:8">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -2316,7 +2316,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:8">
+    <row r="32" spans="1:8">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -2339,7 +2339,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" ht="45" hidden="1" spans="1:7">
+    <row r="33" ht="45" spans="1:7">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -2359,7 +2359,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" ht="60" hidden="1" spans="1:7">
+    <row r="34" ht="60" spans="1:7">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -2379,7 +2379,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="35" ht="30" hidden="1" spans="1:8">
+    <row r="35" ht="30" spans="1:8">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="36" ht="30" hidden="1" spans="1:8">
+    <row r="36" ht="30" spans="1:8">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" ht="30" hidden="1" spans="1:8">
+    <row r="37" ht="30" spans="1:8">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" ht="45" hidden="1" spans="1:7">
+    <row r="38" ht="45" spans="1:7">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" ht="30" hidden="1" spans="1:7">
+    <row r="39" ht="30" spans="1:7">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -2488,7 +2488,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" ht="30" hidden="1" spans="1:7">
+    <row r="40" ht="30" spans="1:7">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" ht="30" hidden="1" spans="1:8">
+    <row r="41" ht="30" spans="1:8">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="42" ht="30" hidden="1" spans="1:8">
+    <row r="42" ht="30" spans="1:8">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="43" ht="30" hidden="1" spans="1:8">
+    <row r="43" ht="30" spans="1:8">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" ht="30" hidden="1" spans="1:7">
+    <row r="44" ht="30" spans="1:7">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" ht="30" hidden="1" spans="1:7">
+    <row r="45" ht="30" spans="1:7">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -2617,7 +2617,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" ht="30" hidden="1" spans="1:7">
+    <row r="46" ht="30" spans="1:7">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -2640,7 +2640,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="47" ht="30" hidden="1" spans="1:8">
+    <row r="47" ht="30" spans="1:8">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -2663,7 +2663,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="48" ht="45" hidden="1" spans="1:7">
+    <row r="48" ht="45" spans="1:7">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -2683,7 +2683,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" ht="30" hidden="1" spans="1:8">
+    <row r="49" ht="30" spans="1:8">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -2703,7 +2703,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="50" ht="30" hidden="1" spans="1:7">
+    <row r="50" ht="30" spans="1:7">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -2723,7 +2723,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="51" ht="30" hidden="1" spans="1:7">
+    <row r="51" ht="30" spans="1:7">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" ht="30" hidden="1" spans="1:7">
+    <row r="52" ht="30" spans="1:7">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -2766,7 +2766,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" ht="30" hidden="1" spans="1:8">
+    <row r="53" ht="30" spans="1:8">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" ht="45" hidden="1" spans="1:7">
+    <row r="55" ht="45" spans="1:7">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -2832,7 +2832,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" ht="45" hidden="1" spans="1:8">
+    <row r="56" ht="45" spans="1:8">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -2855,7 +2855,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" ht="30" hidden="1" spans="1:7">
+    <row r="57" ht="30" spans="1:7">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -2875,7 +2875,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" ht="30" hidden="1" spans="1:8">
+    <row r="58" ht="30" spans="1:8">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="59" ht="30" hidden="1" spans="1:7">
+    <row r="59" ht="30" spans="1:7">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -2915,7 +2915,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" ht="30" hidden="1" spans="1:8">
+    <row r="60" ht="30" spans="1:8">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="61" hidden="1" spans="1:8">
+    <row r="61" spans="1:8">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="62" hidden="1" spans="1:8">
+    <row r="62" spans="1:8">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -2978,7 +2978,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="63" ht="30" hidden="1" spans="1:8">
+    <row r="63" ht="30" spans="1:8">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -3004,7 +3004,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="64" hidden="1" spans="1:8">
+    <row r="64" spans="1:8">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="65" ht="45" hidden="1" spans="1:8">
+    <row r="65" ht="45" spans="1:8">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" hidden="1" spans="1:7">
+    <row r="66" spans="1:7">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -3070,7 +3070,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="67" hidden="1" spans="1:7">
+    <row r="67" spans="1:7">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -3090,7 +3090,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" ht="45" hidden="1" spans="1:7">
+    <row r="68" ht="45" spans="1:7">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -3110,7 +3110,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="69" ht="45" hidden="1" spans="1:8">
+    <row r="69" ht="45" spans="1:8">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -3133,7 +3133,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="70" ht="30" hidden="1" spans="1:7">
+    <row r="70" ht="30" spans="1:7">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -3153,7 +3153,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="71" ht="30" hidden="1" spans="1:8">
+    <row r="71" ht="30" spans="1:8">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="72" ht="60" hidden="1" spans="1:8">
+    <row r="72" ht="60" spans="1:8">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -3219,7 +3219,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="74" ht="30" hidden="1" spans="1:8">
+    <row r="74" ht="30" spans="1:8">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -3245,7 +3245,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="75" ht="30" hidden="1" spans="1:7">
+    <row r="75" ht="30" spans="1:7">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -3265,7 +3265,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" ht="30" hidden="1" spans="1:7">
+    <row r="76" ht="30" spans="1:7">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -3285,7 +3285,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" ht="30" hidden="1" spans="1:6">
+    <row r="77" ht="30" spans="1:6">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -3302,7 +3302,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="78" ht="30" hidden="1" spans="1:7">
+    <row r="78" ht="30" spans="1:7">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -3322,7 +3322,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:7">
+    <row r="79" spans="1:7">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -3339,7 +3339,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="80" ht="30" hidden="1" spans="1:8">
+    <row r="80" ht="30" spans="1:8">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -3362,7 +3362,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="81" ht="30" hidden="1" spans="1:7">
+    <row r="81" ht="30" spans="1:7">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -3382,7 +3382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" ht="30" hidden="1" spans="1:7">
+    <row r="82" ht="30" spans="1:7">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="83" ht="45" hidden="1" spans="1:8">
+    <row r="83" ht="45" spans="1:8">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -3425,7 +3425,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="84" ht="30" hidden="1" spans="1:8">
+    <row r="84" ht="30" spans="1:8">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -3448,7 +3448,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="85" ht="45" hidden="1" spans="1:8">
+    <row r="85" ht="45" spans="1:8">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -3471,7 +3471,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="86" ht="30" hidden="1" spans="1:7">
+    <row r="86" ht="30" spans="1:7">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -3491,7 +3491,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="87" ht="30" hidden="1" spans="1:8">
+    <row r="87" ht="30" spans="1:8">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -3511,7 +3511,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="88" ht="30" hidden="1" spans="1:8">
+    <row r="88" ht="30" spans="1:8">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:7">
+    <row r="89" spans="1:7">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" ht="30" hidden="1" spans="1:7">
+    <row r="90" ht="30" spans="1:7">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:7">
+    <row r="91" spans="1:7">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -3588,7 +3588,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="1:7">
+    <row r="92" spans="1:7">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" ht="45" hidden="1" spans="1:8">
+    <row r="93" ht="45" spans="1:8">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="94" ht="30" hidden="1" spans="1:8">
+    <row r="94" ht="30" spans="1:8">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -3652,14 +3652,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J94">
-    <filterColumn colId="4">
-      <customFilters>
-        <customFilter operator="equal" val="Surface Reconstruct"/>
-      </customFilters>
-    </filterColumn>
-    <extLst/>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter/>
